--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484551_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484551_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.202299999999999</v>
+        <v>8.572900000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>7.4249</v>
+        <v>6.9441</v>
       </c>
       <c r="F2" t="n">
-        <v>1.7774</v>
+        <v>1.6288</v>
       </c>
       <c r="G2" t="n">
         <v>1.7328</v>
@@ -610,13 +610,13 @@
         <v>2.1991</v>
       </c>
       <c r="S2" t="n">
-        <v>1.7523</v>
+        <v>1.1229</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6946</v>
+        <v>0.2138</v>
       </c>
       <c r="U2" t="n">
-        <v>1.0577</v>
+        <v>0.9091</v>
       </c>
       <c r="V2" t="n">
         <v>4.4344</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>8.0436</v>
+        <v>7.2466</v>
       </c>
       <c r="E3" t="n">
-        <v>7.7502</v>
+        <v>7.0771</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2934</v>
+        <v>0.1695</v>
       </c>
       <c r="G3" t="n">
         <v>4.0449</v>
@@ -688,13 +688,13 @@
         <v>2.3823</v>
       </c>
       <c r="S3" t="n">
-        <v>1.5667</v>
+        <v>0.7698</v>
       </c>
       <c r="T3" t="n">
-        <v>1.0053</v>
+        <v>0.3322</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5614</v>
+        <v>0.4376</v>
       </c>
       <c r="V3" t="n">
         <v>0.9658</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>H. BAEZA CABRERA</t>
+          <t>L. RODRIGUEZ CAMPIÑA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0255</v>
+        <v>1.6005</v>
       </c>
       <c r="E4" t="n">
-        <v>2.3505</v>
+        <v>1.6005</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.325</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2633</v>
+        <v>1.6005</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.2497</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>1.513</v>
+        <v>0.6251</v>
       </c>
       <c r="J4" t="n">
-        <v>1.1319</v>
+        <v>1.6005</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.285</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="L4" t="n">
-        <v>1.4169</v>
+        <v>0.6251</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.8686</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.9647</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0961</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5498</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.5498</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1.5345</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8967000000000001</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6378</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.3219</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.6439</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L. RODRIGUEZ CAMPIÑA</t>
+          <t>E. CHOFRE TARREGA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6005</v>
+        <v>1.386</v>
       </c>
       <c r="E5" t="n">
-        <v>1.6005</v>
+        <v>2.2101</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>-0.824</v>
       </c>
       <c r="G5" t="n">
-        <v>1.6005</v>
+        <v>1.7163</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9752999999999999</v>
+        <v>0.7383999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6251</v>
+        <v>0.9779</v>
       </c>
       <c r="J5" t="n">
-        <v>1.6005</v>
+        <v>1.8478</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9752999999999999</v>
+        <v>1.062</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6251</v>
+        <v>0.7857</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>-0.1315</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>-0.3237</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>0.1922</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>0.733</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>0.733</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-0.1182</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>0.0404</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>-0.1586</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.945</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.3219</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>E. CHOFRE TARREGA</t>
+          <t>H. BAEZA CABRERA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9686</v>
+        <v>0.8902</v>
       </c>
       <c r="E6" t="n">
-        <v>1.6192</v>
+        <v>1.6363</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.6506</v>
+        <v>-0.7461</v>
       </c>
       <c r="G6" t="n">
-        <v>1.7163</v>
+        <v>0.2633</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7383999999999999</v>
+        <v>-1.2497</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9779</v>
+        <v>1.513</v>
       </c>
       <c r="J6" t="n">
-        <v>1.8478</v>
+        <v>1.1319</v>
       </c>
       <c r="K6" t="n">
-        <v>1.062</v>
+        <v>-0.285</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7857</v>
+        <v>1.4169</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1315</v>
+        <v>-0.8686</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3237</v>
+        <v>-0.9647</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1922</v>
+        <v>0.0961</v>
       </c>
       <c r="P6" t="n">
-        <v>0.733</v>
+        <v>0.5498</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.733</v>
+        <v>0.5498</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5357</v>
+        <v>0.3991</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5505</v>
+        <v>0.1825</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0148</v>
+        <v>0.2166</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.945</v>
+        <v>-0.3219</v>
       </c>
       <c r="W6" t="n">
         <v>0.3219</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.267</v>
+        <v>-0.6439</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.8636</v>
+        <v>-0.4705</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1184</v>
+        <v>0.4619</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.982</v>
+        <v>-0.9325</v>
       </c>
       <c r="G7" t="n">
         <v>-0.3002</v>
@@ -1000,13 +1000,13 @@
         <v>2.3823</v>
       </c>
       <c r="S7" t="n">
-        <v>0.125</v>
+        <v>0.5181</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2767</v>
+        <v>0.0668</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4018</v>
+        <v>0.4513</v>
       </c>
       <c r="V7" t="n">
         <v>-0.3219</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.4971</v>
+        <v>-0.9252</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.3349</v>
+        <v>-0.9363</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1622</v>
+        <v>0.0112</v>
       </c>
       <c r="G8" t="n">
         <v>-0.0886</v>
@@ -1078,13 +1078,13 @@
         <v>1.2828</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.9658</v>
+        <v>-0.3939</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7707000000000001</v>
+        <v>-0.3722</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1951</v>
+        <v>-0.0217</v>
       </c>
       <c r="V8" t="n">
         <v>2.8559</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>L. RODRIGUEZ CAMPINA</t>
+          <t>H. FABREGAT LORES</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.8292</v>
+        <v>-1.3515</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.2358</v>
+        <v>-0.4162</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4065</v>
+        <v>-0.9353</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.9222</v>
+        <v>-0.4023</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.4121</v>
+        <v>1.3964</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.5101</v>
+        <v>-1.7987</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.0427</v>
+        <v>0.8988</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.5266999999999999</v>
+        <v>1.4148</v>
       </c>
       <c r="L9" t="n">
         <v>-0.516</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.8795</v>
+        <v>-1.3011</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8854</v>
+        <v>-0.0184</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.9941</v>
+        <v>-1.2827</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1833</v>
+        <v>-0.3665</v>
       </c>
       <c r="Q9" t="n">
         <v>-1.8326</v>
       </c>
       <c r="R9" t="n">
-        <v>2.0158</v>
+        <v>1.4661</v>
       </c>
       <c r="S9" t="n">
-        <v>1.2317</v>
+        <v>0.3624</v>
       </c>
       <c r="T9" t="n">
-        <v>0.6395</v>
+        <v>0.1957</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5921</v>
+        <v>0.1666</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.3219</v>
+        <v>-0.945</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.3219</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.3219</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>H. FABREGAT LORES</t>
+          <t>L. RODRIGUEZ CAMPINA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.3218</v>
+        <v>-2.0711</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.0892</v>
+        <v>-2.4281</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.2326</v>
+        <v>0.357</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.4023</v>
+        <v>-2.9222</v>
       </c>
       <c r="H10" t="n">
-        <v>1.3964</v>
+        <v>-1.4121</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.7987</v>
+        <v>-1.5101</v>
       </c>
       <c r="J10" t="n">
-        <v>0.8988</v>
+        <v>-1.0427</v>
       </c>
       <c r="K10" t="n">
-        <v>1.4148</v>
+        <v>-0.5266999999999999</v>
       </c>
       <c r="L10" t="n">
         <v>-0.516</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.3011</v>
+        <v>-1.8795</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.0184</v>
+        <v>-0.8854</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.2827</v>
+        <v>-0.9941</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.3665</v>
+        <v>0.1833</v>
       </c>
       <c r="Q10" t="n">
         <v>-1.8326</v>
       </c>
       <c r="R10" t="n">
-        <v>1.4661</v>
+        <v>2.0158</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.608</v>
+        <v>0.9898</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4774</v>
+        <v>0.4472</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1306</v>
+        <v>0.5426</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.945</v>
+        <v>-0.3219</v>
       </c>
       <c r="W10" t="n">
-        <v>0.3219</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.267</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.5186</v>
+        <v>-2.0923</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.1888</v>
+        <v>0.1136</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.3298</v>
+        <v>-2.2059</v>
       </c>
       <c r="G11" t="n">
         <v>-0.7685</v>
@@ -1312,13 +1312,13 @@
         <v>0.733</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.9438</v>
+        <v>-0.5175</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7157</v>
+        <v>-0.4133</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2281</v>
+        <v>-0.1043</v>
       </c>
       <c r="V11" t="n">
         <v>-0.6231</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.603</v>
+        <v>-3.0281</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.9033</v>
+        <v>-0.6009</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.6997</v>
+        <v>-2.4272</v>
       </c>
       <c r="G12" t="n">
         <v>-0.7477</v>
@@ -1390,13 +1390,13 @@
         <v>0.9163</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9548</v>
+        <v>-0.3799</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5505</v>
+        <v>-0.2481</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4043</v>
+        <v>-0.1318</v>
       </c>
       <c r="V12" t="n">
         <v>-1.9005</v>
@@ -1423,22 +1423,22 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>9.207200000000002</v>
+        <v>9.757500000000002</v>
       </c>
       <c r="E13" t="n">
-        <v>15.1117</v>
+        <v>15.6621</v>
       </c>
       <c r="F13" t="n">
-        <v>-5.9046</v>
+        <v>-5.904500000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>4.128299999999999</v>
+        <v>4.128300000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>4.9299</v>
+        <v>4.929899999999998</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.8017000000000004</v>
+        <v>-0.8017</v>
       </c>
       <c r="J13" t="n">
         <v>19.3577</v>
@@ -1447,7 +1447,7 @@
         <v>14.8673</v>
       </c>
       <c r="L13" t="n">
-        <v>4.489999999999999</v>
+        <v>4.49</v>
       </c>
       <c r="M13" t="n">
         <v>-15.2293</v>
@@ -1456,10 +1456,10 @@
         <v>-9.9374</v>
       </c>
       <c r="O13" t="n">
-        <v>-5.291800000000001</v>
+        <v>-5.291799999999999</v>
       </c>
       <c r="P13" t="n">
-        <v>9.999999999962816e-05</v>
+        <v>0.000100000000000211</v>
       </c>
       <c r="Q13" t="n">
         <v>-14.6607</v>
@@ -1468,13 +1468,13 @@
         <v>14.6605</v>
       </c>
       <c r="S13" t="n">
-        <v>2.202100000000001</v>
+        <v>2.7526</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1054000000000002</v>
+        <v>0.4450000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>2.3075</v>
+        <v>2.3074</v>
       </c>
       <c r="V13" t="n">
         <v>2.876799999999999</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.4122</v>
+        <v>1.7793</v>
       </c>
       <c r="E14" t="n">
-        <v>5.4988</v>
+        <v>5.7872</v>
       </c>
       <c r="F14" t="n">
-        <v>-4.0866</v>
+        <v>-4.0079</v>
       </c>
       <c r="G14" t="n">
         <v>5.3542</v>
@@ -1546,13 +1546,13 @@
         <v>1.6493</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.3158</v>
+        <v>-0.9487</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.0098</v>
+        <v>-0.7213000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3061</v>
+        <v>-0.2274</v>
       </c>
       <c r="V14" t="n">
         <v>-1.5266</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>C. FAJARDO PAÑOS</t>
+          <t>G. CASASUS GOYENECHE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9502</v>
+        <v>0.9814000000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9502</v>
+        <v>1.36</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>-0.3787</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9502</v>
+        <v>0.9348</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3251</v>
+        <v>0.9573</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6251</v>
+        <v>-0.0226</v>
       </c>
       <c r="J15" t="n">
-        <v>0.9502</v>
+        <v>1.2646</v>
       </c>
       <c r="K15" t="n">
-        <v>0.3251</v>
+        <v>1.223</v>
       </c>
       <c r="L15" t="n">
-        <v>0.6251</v>
+        <v>0.0417</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>-0.3299</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>-0.2656</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>-0.0643</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>0.5498</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>0.5498</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>0.4627</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>0.0954</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>0.3673</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>-0.9658</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.9658</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. JIMENEZ LORENTE</t>
+          <t>C. FAJARDO PAÑOS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5416</v>
+        <v>0.9502</v>
       </c>
       <c r="E16" t="n">
-        <v>2.4164</v>
+        <v>0.9502</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.8748</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2086</v>
+        <v>0.9502</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3435</v>
+        <v>0.3251</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1349</v>
+        <v>0.6251</v>
       </c>
       <c r="J16" t="n">
-        <v>4.0204</v>
+        <v>0.9502</v>
       </c>
       <c r="K16" t="n">
-        <v>2.5201</v>
+        <v>0.3251</v>
       </c>
       <c r="L16" t="n">
-        <v>1.5003</v>
+        <v>0.6251</v>
       </c>
       <c r="M16" t="n">
-        <v>-3.8118</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>-2.1766</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.6351</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>0.3665</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.8326</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.1991</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4074</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.405</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0024</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>0.3738</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0.6335</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2596</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. FERNANDEZ NARRO</t>
+          <t>J. JIMENEZ LORENTE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4478</v>
+        <v>0.4309</v>
       </c>
       <c r="E17" t="n">
-        <v>1.1547</v>
+        <v>2.1279</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.7069</v>
+        <v>-1.697</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0138</v>
+        <v>0.2086</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1646</v>
+        <v>0.3435</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1508</v>
+        <v>-0.1349</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2551</v>
+        <v>4.0204</v>
       </c>
       <c r="K17" t="n">
-        <v>0.2135</v>
+        <v>2.5201</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0417</v>
+        <v>1.5003</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.2413</v>
+        <v>-3.8118</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.0489</v>
+        <v>-2.1766</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1925</v>
+        <v>-1.6351</v>
       </c>
       <c r="P17" t="n">
-        <v>0.733</v>
+        <v>0.3665</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.8326</v>
       </c>
       <c r="R17" t="n">
-        <v>0.733</v>
+        <v>2.1991</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3241</v>
+        <v>-0.5181</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2557</v>
+        <v>-0.6934</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0684</v>
+        <v>0.1753</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.6231</v>
+        <v>0.3738</v>
       </c>
       <c r="W17" t="n">
-        <v>0.6439</v>
+        <v>0.6335</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.267</v>
+        <v>-0.2596</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>G. CASASUS GOYENECHE</t>
+          <t>D. FERNANDEZ NARRO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4015</v>
+        <v>0.426</v>
       </c>
       <c r="E18" t="n">
-        <v>0.8793</v>
+        <v>1.0586</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4778</v>
+        <v>-0.6326000000000001</v>
       </c>
       <c r="G18" t="n">
-        <v>0.9348</v>
+        <v>0.0138</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9573</v>
+        <v>0.1646</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.0226</v>
+        <v>-0.1508</v>
       </c>
       <c r="J18" t="n">
-        <v>1.2646</v>
+        <v>0.2551</v>
       </c>
       <c r="K18" t="n">
-        <v>1.223</v>
+        <v>0.2135</v>
       </c>
       <c r="L18" t="n">
         <v>0.0417</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.3299</v>
+        <v>-0.2413</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2656</v>
+        <v>-0.0489</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.0643</v>
+        <v>-0.1925</v>
       </c>
       <c r="P18" t="n">
-        <v>0.5498</v>
+        <v>0.733</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.5498</v>
+        <v>0.733</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1172</v>
+        <v>0.3022</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3854</v>
+        <v>0.1595</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2682</v>
+        <v>0.1427</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.9658</v>
+        <v>-0.6231</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.6439</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.9658</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. HERRANDO CUENCA</t>
+          <t>C. FAJARDO PANOS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4677</v>
+        <v>-0.179</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2817</v>
+        <v>-0.5589</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.7493</v>
+        <v>0.3799</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.4137</v>
+        <v>-0.8305</v>
       </c>
       <c r="H19" t="n">
-        <v>0.5962</v>
+        <v>-1.3401</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.0099</v>
+        <v>0.5096000000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.29</v>
+        <v>-0.9311</v>
       </c>
       <c r="K19" t="n">
-        <v>0.9504</v>
+        <v>-0.4151</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.2404</v>
+        <v>-0.516</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.1237</v>
+        <v>0.1006</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3541</v>
+        <v>-0.925</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.7695</v>
+        <v>1.0256</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.3665</v>
+        <v>-0.1833</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.8326</v>
+        <v>-0.9163</v>
       </c>
       <c r="R19" t="n">
-        <v>1.4661</v>
+        <v>0.733</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2556</v>
+        <v>-0.1103</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1297</v>
+        <v>0.0215</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1259</v>
+        <v>-0.1318</v>
       </c>
       <c r="V19" t="n">
-        <v>1.5681</v>
+        <v>0.945</v>
       </c>
       <c r="W19" t="n">
-        <v>2.5339</v>
+        <v>1.267</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.9658</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>V. PRADA SANCHEZ</t>
+          <t>S. HERRANDO CUENCA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5002</v>
+        <v>-0.2447</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.5419</v>
+        <v>0.2817</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0417</v>
+        <v>-0.5264</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.3219</v>
+        <v>-1.4137</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.011</v>
+        <v>0.5962</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3108</v>
+        <v>-2.0099</v>
       </c>
       <c r="J20" t="n">
-        <v>1.8246</v>
+        <v>-0.29</v>
       </c>
       <c r="K20" t="n">
-        <v>2.2633</v>
+        <v>0.9504</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.4387</v>
+        <v>-1.2404</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.1465</v>
+        <v>-1.1237</v>
       </c>
       <c r="N20" t="n">
-        <v>-2.2744</v>
+        <v>-0.3541</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1279</v>
+        <v>-0.7695</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.1833</v>
+        <v>-0.3665</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.7489</v>
+        <v>-1.8326</v>
       </c>
       <c r="R20" t="n">
-        <v>2.5656</v>
+        <v>1.4661</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0574</v>
+        <v>-0.0326</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3824</v>
+        <v>-0.1297</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4398</v>
+        <v>0.09710000000000001</v>
       </c>
       <c r="V20" t="n">
-        <v>0.0623</v>
+        <v>1.5681</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2.5339</v>
       </c>
       <c r="X20" t="n">
-        <v>0.0623</v>
+        <v>-0.9658</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>C. FAJARDO PANOS</t>
+          <t>V. PRADA SANCHEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.9323</v>
+        <v>-0.7318</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.0397</v>
+        <v>-0.9265</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1074</v>
+        <v>0.1947</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.8305</v>
+        <v>-0.3219</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.3401</v>
+        <v>-0.011</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5096000000000001</v>
+        <v>-0.3108</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.9311</v>
+        <v>1.8246</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.4151</v>
+        <v>2.2633</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.516</v>
+        <v>-0.4387</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1006</v>
+        <v>-2.1465</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.925</v>
+        <v>-2.2744</v>
       </c>
       <c r="O21" t="n">
-        <v>1.0256</v>
+        <v>0.1279</v>
       </c>
       <c r="P21" t="n">
         <v>-0.1833</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9163</v>
+        <v>-2.7489</v>
       </c>
       <c r="R21" t="n">
-        <v>0.733</v>
+        <v>2.5656</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8636</v>
+        <v>-0.289</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4593</v>
+        <v>-0.0022</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4043</v>
+        <v>-0.2868</v>
       </c>
       <c r="V21" t="n">
-        <v>0.945</v>
+        <v>0.0623</v>
       </c>
       <c r="W21" t="n">
-        <v>1.267</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.3219</v>
+        <v>0.0623</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.1089</v>
+        <v>-1.3289</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.5931999999999999</v>
+        <v>-0.6894</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.5157</v>
+        <v>-0.6395999999999999</v>
       </c>
       <c r="G22" t="n">
         <v>-0.5392</v>
@@ -2170,13 +2170,13 @@
         <v>0.5498</v>
       </c>
       <c r="S22" t="n">
-        <v>0.4302</v>
+        <v>0.2102</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2949</v>
+        <v>-0.391</v>
       </c>
       <c r="U22" t="n">
-        <v>0.7251</v>
+        <v>0.6012</v>
       </c>
       <c r="V22" t="n">
         <v>-0.6335</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.7713</v>
+        <v>-3.326</v>
       </c>
       <c r="E23" t="n">
-        <v>2.123</v>
+        <v>1.2576</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.8943</v>
+        <v>-4.5836</v>
       </c>
       <c r="G23" t="n">
         <v>-2.2061</v>
@@ -2248,13 +2248,13 @@
         <v>2.3823</v>
       </c>
       <c r="S23" t="n">
-        <v>1.6737</v>
+        <v>0.119</v>
       </c>
       <c r="T23" t="n">
-        <v>0.6931</v>
+        <v>-0.1723</v>
       </c>
       <c r="U23" t="n">
-        <v>0.9806</v>
+        <v>0.2913</v>
       </c>
       <c r="V23" t="n">
         <v>-0.8723</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-8.18</v>
+        <v>-7.3233</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.2246</v>
+        <v>-4.7439</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.9554</v>
+        <v>-2.5794</v>
       </c>
       <c r="G24" t="n">
         <v>-6.2785</v>
@@ -2326,13 +2326,13 @@
         <v>1.8326</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.6131</v>
+        <v>-0.7564</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.9547</v>
+        <v>-0.474</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.6584</v>
+        <v>-0.2824</v>
       </c>
       <c r="V24" t="n">
         <v>-1.2047</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-9.207100000000001</v>
+        <v>-8.565899999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>5.904700000000001</v>
+        <v>5.904500000000002</v>
       </c>
       <c r="F25" t="n">
-        <v>-15.1117</v>
+        <v>-14.4706</v>
       </c>
       <c r="G25" t="n">
         <v>-4.1283</v>
@@ -2383,7 +2383,7 @@
         <v>9.9375</v>
       </c>
       <c r="L25" t="n">
-        <v>5.2919</v>
+        <v>5.291900000000002</v>
       </c>
       <c r="M25" t="n">
         <v>-19.3576</v>
@@ -2395,7 +2395,7 @@
         <v>-4.4902</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.110223024625157e-16</v>
+        <v>1.110223024625157e-16</v>
       </c>
       <c r="Q25" t="n">
         <v>-14.6608</v>
@@ -2404,16 +2404,16 @@
         <v>14.6606</v>
       </c>
       <c r="S25" t="n">
-        <v>-2.2021</v>
+        <v>-1.561</v>
       </c>
       <c r="T25" t="n">
-        <v>-2.3076</v>
+        <v>-2.3075</v>
       </c>
       <c r="U25" t="n">
-        <v>0.1053999999999999</v>
+        <v>0.7465000000000002</v>
       </c>
       <c r="V25" t="n">
-        <v>-2.8768</v>
+        <v>-2.876799999999999</v>
       </c>
       <c r="W25" t="n">
         <v>7.6435</v>
